--- a/engagement_survey_forms/021_employee_transfer_and_pay_rate_survey--engagement_survey_forms.xlsx
+++ b/engagement_survey_forms/021_employee_transfer_and_pay_rate_survey--engagement_survey_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,40 +515,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey</t>
+          <t>transfer_category</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Employee Transfer And Pay Rate Survey</t>
+          <t>Which category does this transfer belong to?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_2</t>
+          <t>employee_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>What is the employee's name?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,67 +561,67 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_3</t>
+          <t>transfer_type</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Use the Employee Transfer and Pay Rate Survey form template from Jotform to streamline internal transfer reviews and pay changes with Jotform Form Builder, drag-and-drop interface, and organized data collection.</t>
-        </is>
-      </c>
+          <t>What type of transfer is this?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_4</t>
+          <t>pay_change</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Employee</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Is this transfer for a pay change?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>yes/no</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_5</t>
+          <t>date_of_transfer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Transfer Type</t>
+          <t>On what date did the pay change occur?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -639,18 +639,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_6</t>
+          <t>old_pay_rate</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pay Change</t>
+          <t>What was the old pay rate?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -662,12 +662,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_7</t>
+          <t>new_pay_rate</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pay Rate</t>
+          <t>What is the new pay rate?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -680,17 +680,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_8</t>
+          <t>reason_for_pay_change</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>What is the reason for the pay change?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,23 +703,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_9</t>
+          <t>impact_on_schedule</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>What is the impact on the employee's work schedule?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -731,12 +731,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_10</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Are there any comments about the transfer or pay change?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -754,12 +754,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_11</t>
+          <t>transfer_category_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>What is the category of the transfer?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -772,322 +772,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_12</t>
+          <t>is_transfer_approved</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Is the transfer approved?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>yes/no</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1102,12 +807,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1130,510 +835,170 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_2_choices</t>
+          <t>transfer_category_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'engagement_survey_forms'}</t>
+          <t>employee_development</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Engagement Survey Forms'}</t>
+          <t>Employee Development</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_2_choices</t>
+          <t>transfer_category_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_4_choices</t>
+          <t>transfer_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'jane_doe'}</t>
+          <t>internal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Jane Doe'}</t>
+          <t>Internal</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_4_choices</t>
+          <t>transfer_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'john_doe'}</t>
+          <t>external</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'John Doe'}</t>
+          <t>External</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_5_choices</t>
+          <t>pay_change_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'internal'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Internal'}</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_5_choices</t>
+          <t>pay_change_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'external'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'External'}</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_11_choices</t>
+          <t>transfer_category_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'employee_development'}</t>
+          <t>employee_development</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Employee Development'}</t>
+          <t>Employee Development</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_11_choices</t>
+          <t>transfer_category_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_15_choices</t>
+          <t>is_transfer_approved_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'employee_development'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Employee Development'}</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>employee_transfer_and_pay_rate_survey_15_choices</t>
+          <t>is_transfer_approved_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'other'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_16_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'name':_'employee_development'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'name': 'Employee Development'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_16_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'name':_'other'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'name': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_17_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'name':_'employee_development'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'name': 'Employee Development'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_17_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'name':_'other'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'name': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_18_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'name':_'employee_development'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'name': 'Employee Development'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_18_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'name':_'other'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'name': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_19_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'name':_'employee_development'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'name': 'Employee Development'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_19_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'name':_'other'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'name': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_20_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'name':_'employee_development'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'name': 'Employee Development'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_20_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'name':_'other'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'name': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_21_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'name':_'employee_development'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'name': 'Employee Development'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_21_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'name':_'other'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'name': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_22_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'name':_'employee_development'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'name': 'Employee Development'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_22_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'name':_'other'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'name': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_23_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'name':_'employee_development'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'name': 'Employee Development'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_23_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'name':_'other'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'name': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_24_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'name':_'employee_development'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'name': 'Employee Development'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_24_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'name':_'other'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'name': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_25_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'name':_'employee_development'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'name': 'Employee Development'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>employee_transfer_and_pay_rate_survey_25_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'name':_'other'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'name': 'Other'}</t>
+          <t>no</t>
         </is>
       </c>
     </row>
